--- a/artfynd/A 31504-2025 artfynd.xlsx
+++ b/artfynd/A 31504-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105165248</v>
+        <v>105165247</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608355.7981420509</v>
+        <v>608362</v>
       </c>
       <c r="R2" t="n">
-        <v>7038741.353283934</v>
+        <v>7038733</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105165246</v>
+        <v>105165248</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608358.0593334748</v>
+        <v>608356</v>
       </c>
       <c r="R3" t="n">
-        <v>7038727.555768295</v>
+        <v>7038741</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105165244</v>
+        <v>105165250</v>
       </c>
       <c r="B4" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608309.3722286229</v>
+        <v>608369</v>
       </c>
       <c r="R4" t="n">
-        <v>7038722.76984802</v>
+        <v>7038734</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105165243</v>
+        <v>105165241</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608334.0835989458</v>
+        <v>608344</v>
       </c>
       <c r="R5" t="n">
-        <v>7038747.329308303</v>
+        <v>7038787</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,24 +1046,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105165250</v>
+        <v>105165249</v>
       </c>
       <c r="B6" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608369.0227181192</v>
+        <v>608374</v>
       </c>
       <c r="R6" t="n">
-        <v>7038734.641476926</v>
+        <v>7038733</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,19 +1147,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105165242</v>
+        <v>105165246</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608276.9599544375</v>
+        <v>608358</v>
       </c>
       <c r="R7" t="n">
-        <v>7038753.446351235</v>
+        <v>7038727</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1333,19 +1248,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105165247</v>
+        <v>105165242</v>
       </c>
       <c r="B8" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608361.890775569</v>
+        <v>608277</v>
       </c>
       <c r="R8" t="n">
-        <v>7038733.504147564</v>
+        <v>7038753</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1449,19 +1349,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105165241</v>
+        <v>105165239</v>
       </c>
       <c r="B9" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1532,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>608344.3865021784</v>
+        <v>608385</v>
       </c>
       <c r="R9" t="n">
-        <v>7038787.063832968</v>
+        <v>7038768</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1565,19 +1450,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,37 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105165249</v>
+        <v>105165244</v>
       </c>
       <c r="B10" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1648,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608374.022720955</v>
+        <v>608309</v>
       </c>
       <c r="R10" t="n">
-        <v>7038732.57350263</v>
+        <v>7038723</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1681,19 +1551,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,12 +1587,7 @@
         <v>105165245</v>
       </c>
       <c r="B11" t="n">
-        <v>56286</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1604,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1764,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608353.7343165962</v>
+        <v>608354</v>
       </c>
       <c r="R11" t="n">
-        <v>7038749.339218968</v>
+        <v>7038750</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1797,19 +1652,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1838,6 +1683,112 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>105165243</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>608334</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7038747</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett tjugotal</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
         </is>

--- a/artfynd/A 31504-2025 artfynd.xlsx
+++ b/artfynd/A 31504-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165247</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165248</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165250</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165241</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165249</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165246</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165242</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165239</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165244</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165245</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,8 +1848,26 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165243</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>